--- a/CRISIS_SCENARIO_(High_Load)_-_Topology-Aware_GPR_Results.xlsx
+++ b/CRISIS_SCENARIO_(High_Load)_-_Topology-Aware_GPR_Results.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f.oeczan\PycharmProjects\SimBench-Netz_2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839BB55D-2C8E-453A-9A4C-C1AE5CF6F7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -375,8 +364,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,33 +417,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -496,7 +474,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -528,27 +506,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -580,24 +540,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -773,18 +715,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,623 +739,623 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" spans="1:6">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:6">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:6">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:6">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" spans="1:6">
+      <c r="A7">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" spans="1:6">
+      <c r="A8">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" spans="1:6">
+      <c r="A9">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="10" spans="1:6">
+      <c r="A10">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="11" spans="1:6">
+      <c r="A11">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>15</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="14" spans="1:6">
+      <c r="A14">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>18</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="16" spans="1:6">
+      <c r="A16">
         <v>19</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>86</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="17" spans="1:6">
+      <c r="A17">
         <v>20</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="18" spans="1:6">
+      <c r="A18">
         <v>21</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="19" spans="1:6">
+      <c r="A19">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="20" spans="1:6">
+      <c r="A20">
         <v>23</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="21" spans="1:6">
+      <c r="A21">
         <v>26</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="22" spans="1:6">
+      <c r="A22">
         <v>28</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="23" spans="1:6">
+      <c r="A23">
         <v>29</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="24" spans="1:6">
+      <c r="A24">
         <v>30</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>85</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="25" spans="1:6">
+      <c r="A25">
         <v>32</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>92</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="26" spans="1:6">
+      <c r="A26">
         <v>33</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>93</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="27" spans="1:6">
+      <c r="A27">
         <v>35</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="28" spans="1:6">
+      <c r="A28">
         <v>38</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+    <row r="29" spans="1:6">
+      <c r="A29">
         <v>39</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="30" spans="1:6">
+      <c r="A30">
         <v>41</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="31" spans="1:6">
+      <c r="A31">
         <v>42</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="32" spans="1:6">
+      <c r="A32">
         <v>129</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
         <v>75</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>96</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" t="s">
         <v>112</v>
       </c>
     </row>
